--- a/AAII_Financials/Yearly/FPAFY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FPAFY_YR_FIN.xlsx
@@ -2972,7 +2972,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2526500</v>
+        <v>2550000</v>
       </c>
       <c r="E58" s="3">
         <v>2548700</v>
@@ -3023,7 +3023,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1222900</v>
+        <v>1199400</v>
       </c>
       <c r="E59" s="3">
         <v>1005600</v>
@@ -3125,7 +3125,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10487600</v>
+        <v>10524800</v>
       </c>
       <c r="E61" s="3">
         <v>9987600</v>
@@ -3176,7 +3176,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1160300</v>
+        <v>1123100</v>
       </c>
       <c r="E62" s="3">
         <v>1252300</v>
